--- a/REACT-KHACHSAN-VT/public/buongphong/template-import.xlsx
+++ b/REACT-KHACHSAN-VT/public/buongphong/template-import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckhan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\FE-QUANLY-KHACHSAN-VT\REACT-KHACHSAN-VT\public\buongphong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA660BA-740E-4D96-91E6-B30C04B5FF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAE2AA0-B397-4C52-9595-90B0225C314E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="4510" windowWidth="19450" windowHeight="14060" xr2:uid="{BAC1294F-67BD-44E7-AACA-787A2ED500C0}"/>
+    <workbookView xWindow="7490" yWindow="3450" windowWidth="28800" windowHeight="15290" xr2:uid="{BAC1294F-67BD-44E7-AACA-787A2ED500C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>STT</t>
   </si>
@@ -51,21 +51,6 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>SP001</t>
-  </si>
-  <si>
-    <t>Dầu gọi</t>
-  </si>
-  <si>
-    <t>ĐVT</t>
-  </si>
-  <si>
-    <t>Bịch</t>
-  </si>
-  <si>
-    <t>SP002</t>
-  </si>
-  <si>
     <t>Sữa tắm</t>
   </si>
   <si>
@@ -75,13 +60,94 @@
     <t>7 up</t>
   </si>
   <si>
-    <t>SP003</t>
-  </si>
-  <si>
-    <t>SP004</t>
-  </si>
-  <si>
-    <t>Lon</t>
+    <t>TAM_BONG</t>
+  </si>
+  <si>
+    <t>Tăm bông</t>
+  </si>
+  <si>
+    <t>NUOC_RUA_TAY</t>
+  </si>
+  <si>
+    <t>Nước rửa tay</t>
+  </si>
+  <si>
+    <t>DAU_GOI</t>
+  </si>
+  <si>
+    <t>Dầu gội</t>
+  </si>
+  <si>
+    <t>SUA_TAM</t>
+  </si>
+  <si>
+    <t>GIAY_VE_SINH_BLESSYOU</t>
+  </si>
+  <si>
+    <t>Giấy vệ sinh blessyou</t>
+  </si>
+  <si>
+    <t>KHAN_LAU_TAY_BLESSYOU</t>
+  </si>
+  <si>
+    <t>Khăn lau tay blessyou</t>
+  </si>
+  <si>
+    <t>7UP</t>
+  </si>
+  <si>
+    <t>PEPSI</t>
+  </si>
+  <si>
+    <t>NUOC_SUOI_355</t>
+  </si>
+  <si>
+    <t>Nuoc suối (355ml)</t>
+  </si>
+  <si>
+    <t>LUOC</t>
+  </si>
+  <si>
+    <t>Lược</t>
+  </si>
+  <si>
+    <t>DAI_CAO</t>
+  </si>
+  <si>
+    <t>Dao cạo</t>
+  </si>
+  <si>
+    <t>CHUP_TOC</t>
+  </si>
+  <si>
+    <t>Chụp tóc</t>
+  </si>
+  <si>
+    <t>BAN_CHAI</t>
+  </si>
+  <si>
+    <t>Bàn chải</t>
+  </si>
+  <si>
+    <t>NUOC_SUOI_500</t>
+  </si>
+  <si>
+    <t>Nước suối (500ml)</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>Trà gói cozy</t>
+  </si>
+  <si>
+    <t>CAPHE</t>
+  </si>
+  <si>
+    <t>Cà phê gói nhỏ</t>
+  </si>
+  <si>
+    <t>Loại</t>
   </si>
 </sst>
 </file>
@@ -151,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -163,9 +229,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,8 +547,8 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" style="5" customWidth="1"/>
     <col min="4" max="5" width="16.453125" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
   </cols>
@@ -504,7 +567,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -514,167 +577,255 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
+      <c r="B3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>12</v>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>

--- a/REACT-KHACHSAN-VT/public/buongphong/template-import.xlsx
+++ b/REACT-KHACHSAN-VT/public/buongphong/template-import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\FE-QUANLY-KHACHSAN-VT\REACT-KHACHSAN-VT\public\buongphong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DAE2AA0-B397-4C52-9595-90B0225C314E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84B8183-832A-43EB-AE17-061EED98E7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7490" yWindow="3450" windowWidth="28800" windowHeight="15290" xr2:uid="{BAC1294F-67BD-44E7-AACA-787A2ED500C0}"/>
+    <workbookView xWindow="1370" yWindow="2920" windowWidth="29010" windowHeight="13680" xr2:uid="{BAC1294F-67BD-44E7-AACA-787A2ED500C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,21 +33,36 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={764BB916-1583-4A25-A903-94A4C67F48D5}</author>
+    <author>tc={A2330C45-9FE9-4D2D-BC40-74961043405F}</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{764BB916-1583-4A25-A903-94A4C67F48D5}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nếu có</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{A2330C45-9FE9-4D2D-BC40-74961043405F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Nếu có</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Mã hàng</t>
-  </si>
-  <si>
-    <t>Tên hàng</t>
-  </si>
-  <si>
-    <t>Số lượng</t>
-  </si>
-  <si>
     <t>Ghi chú</t>
   </si>
   <si>
@@ -147,14 +162,26 @@
     <t>Cà phê gói nhỏ</t>
   </si>
   <si>
-    <t>Loại</t>
+    <t>Tên nhãn hiệu</t>
+  </si>
+  <si>
+    <t>STT(*)</t>
+  </si>
+  <si>
+    <t>Mã hàng(*)</t>
+  </si>
+  <si>
+    <t>Tên hàng(*)</t>
+  </si>
+  <si>
+    <t>Số lượng(*)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +201,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -245,6 +278,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Khang Cao Vủ" id="{8FD9D197-7A86-48F5-A531-25DB6A7EBFDE}" userId="52b49d5359eb3af5" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,8 +581,19 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2026-06-24T02:00:10.08" personId="{8FD9D197-7A86-48F5-A531-25DB6A7EBFDE}" id="{764BB916-1583-4A25-A903-94A4C67F48D5}">
+    <text>Nếu có</text>
+  </threadedComment>
+  <threadedComment ref="F1" dT="2026-06-24T02:00:31.40" personId="{8FD9D197-7A86-48F5-A531-25DB6A7EBFDE}" id="{A2330C45-9FE9-4D2D-BC40-74961043405F}">
+    <text>Nếu có</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1855395-0BA3-4664-8D4E-886AB19B23AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1855395-0BA3-4664-8D4E-886AB19B23AB}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -555,22 +605,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -578,10 +628,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -594,10 +644,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -610,10 +660,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1">
         <v>5</v>
@@ -626,10 +676,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1">
         <v>5</v>
@@ -642,10 +692,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
@@ -658,10 +708,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1">
         <v>5</v>
@@ -674,10 +724,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -690,10 +740,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
@@ -706,10 +756,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>5</v>
@@ -722,10 +772,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1">
         <v>5</v>
@@ -738,10 +788,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
@@ -754,10 +804,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
@@ -770,10 +820,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
@@ -786,10 +836,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1">
         <v>5</v>
@@ -802,10 +852,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1">
         <v>5</v>
@@ -818,10 +868,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D17" s="1">
         <v>5</v>
@@ -832,5 +882,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>